--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-nationality.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:16:59+00:00</t>
+    <t>2026-06-05T12:18:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-nationality.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:18:27+00:00</t>
+    <t>2026-06-05T12:21:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-nationality.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:21:59+00:00</t>
+    <t>2026-06-05T13:35:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
